--- a/product_selector_out/STM8S series.xlsx
+++ b/product_selector_out/STM8S series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AH48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -716,6 +717,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -883,6 +889,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s001j3.pdf</t>
         </is>
       </c>
@@ -1050,6 +1061,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s001j3.pdf</t>
         </is>
       </c>
@@ -1217,6 +1233,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s005c6.pdf</t>
         </is>
       </c>
@@ -1384,6 +1405,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s007c8.pdf</t>
         </is>
       </c>
@@ -1551,6 +1577,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s001j3.pdf</t>
         </is>
       </c>
@@ -1718,6 +1749,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s003f3.pdf</t>
         </is>
       </c>
@@ -1885,6 +1921,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2052,6 +2093,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2219,6 +2265,11 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s105c4.pdf</t>
         </is>
       </c>
@@ -2386,6 +2437,11 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2553,6 +2609,11 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2720,6 +2781,11 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2887,6 +2953,11 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -3054,6 +3125,11 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -3221,6 +3297,11 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -3388,6 +3469,11 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3555,6 +3641,11 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3722,6 +3813,11 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -3889,6 +3985,11 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4056,6 +4157,11 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4223,6 +4329,11 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4390,6 +4501,11 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4557,6 +4673,11 @@
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4724,6 +4845,11 @@
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -4891,6 +5017,11 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -5058,6 +5189,11 @@
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -5225,6 +5361,11 @@
       </c>
       <c r="AG37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -5392,6 +5533,11 @@
       </c>
       <c r="AG38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -5559,6 +5705,11 @@
       </c>
       <c r="AG39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -5726,6 +5877,11 @@
       </c>
       <c r="AG40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -5893,6 +6049,11 @@
       </c>
       <c r="AG41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -6060,6 +6221,11 @@
       </c>
       <c r="AG42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -6227,6 +6393,11 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -6394,6 +6565,11 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -6561,6 +6737,11 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s207mb.pdf</t>
         </is>
       </c>
@@ -6728,6 +6909,11 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s903k3.pdf</t>
         </is>
       </c>
@@ -6895,6 +7081,11 @@
       </c>
       <c r="AG47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s903k3.pdf</t>
         </is>
       </c>
@@ -7062,14 +7253,19 @@
       </c>
       <c r="AG48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8splnb1.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -7122,7 +7318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AH48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7158,6 +7354,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7344,6 +7541,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -7509,7 +7711,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7676,7 +7883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7843,7 +8055,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8010,7 +8227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8177,7 +8399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8344,7 +8571,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8511,7 +8743,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8678,7 +8915,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8845,7 +9087,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9012,7 +9259,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="6" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9179,7 +9431,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9346,7 +9603,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9513,7 +9775,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9680,7 +9947,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9847,7 +10119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10014,7 +10291,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10181,7 +10463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10348,7 +10635,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10515,7 +10807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10682,7 +10979,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10849,7 +11151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG31" s="6" t="inlineStr">
+      <c r="AG31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11016,7 +11323,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG32" s="6" t="inlineStr">
+      <c r="AG32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11183,7 +11495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG33" s="6" t="inlineStr">
+      <c r="AG33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11350,7 +11667,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG34" s="6" t="inlineStr">
+      <c r="AG34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11517,7 +11839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG35" s="6" t="inlineStr">
+      <c r="AG35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11684,7 +12011,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG36" s="6" t="inlineStr">
+      <c r="AG36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11851,7 +12183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG37" s="6" t="inlineStr">
+      <c r="AG37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12018,7 +12355,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG38" s="6" t="inlineStr">
+      <c r="AG38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12185,7 +12527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG39" s="6" t="inlineStr">
+      <c r="AG39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12352,7 +12699,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG40" s="6" t="inlineStr">
+      <c r="AG40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12519,7 +12871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG41" s="6" t="inlineStr">
+      <c r="AG41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12686,7 +13043,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG42" s="6" t="inlineStr">
+      <c r="AG42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12853,7 +13215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG43" s="6" t="inlineStr">
+      <c r="AG43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13020,7 +13387,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG44" s="6" t="inlineStr">
+      <c r="AG44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13187,7 +13559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG45" s="6" t="inlineStr">
+      <c r="AG45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13354,7 +13731,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG46" s="6" t="inlineStr">
+      <c r="AG46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13521,7 +13903,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG47" s="6" t="inlineStr">
+      <c r="AG47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13688,7 +14075,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG48" s="6" t="inlineStr">
+      <c r="AG48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13696,8 +14088,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
